--- a/outputs/forecasts/xgb_forecast_annual.xlsx
+++ b/outputs/forecasts/xgb_forecast_annual.xlsx
@@ -445,7 +445,7 @@
         <v>2026</v>
       </c>
       <c r="B2" t="n">
-        <v>1183820.328125</v>
+        <v>1112980.071055329</v>
       </c>
     </row>
   </sheetData>
